--- a/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la edad en meses en la que empezaron a comer huevo</t>
+          <t>Menores según la edad en meses en la que empezaron a comer huevo (tasa de respuesta: 48,37%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>8,01; 11,63</t>
+          <t>7,81; 11,57</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,27; 12,1</t>
+          <t>10,24; 12,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,42</t>
+          <t>7,75; 10,32</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,39; 13,22</t>
+          <t>10,42; 13,05</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,58; 11,72</t>
+          <t>9,52; 11,67</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,17</t>
+          <t>6,86; 10,2</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,62; 11,92</t>
+          <t>9,45; 11,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,18; 11,64</t>
+          <t>10,19; 11,61</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,65; 9,77</t>
+          <t>7,53; 9,72</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,86</t>
+          <t>8,03; 10,94</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,26; 12,37</t>
+          <t>9,28; 12,32</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,02; 12,25</t>
+          <t>8,98; 12,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,15; 12,71</t>
+          <t>10,2; 12,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,34; 10,72</t>
+          <t>8,39; 10,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,38; 11,57</t>
+          <t>9,33; 11,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,82; 11,99</t>
+          <t>9,79; 11,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,2; 11,14</t>
+          <t>9,13; 11,12</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,54; 11,5</t>
+          <t>9,53; 11,56</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,82; 12,7</t>
+          <t>9,86; 12,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,66; 12,9</t>
+          <t>9,74; 12,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,51; 12,0</t>
+          <t>8,5; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,62; 12,18</t>
+          <t>9,59; 12,34</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,71; 12,01</t>
+          <t>10,69; 12,04</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,43; 15,54</t>
+          <t>10,38; 15,49</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,04</t>
+          <t>10,17; 12,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,52; 11,99</t>
+          <t>10,55; 12,02</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,07; 12,9</t>
+          <t>10,11; 12,93</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,31; 12,52</t>
+          <t>9,55; 12,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,79; 12,25</t>
+          <t>10,78; 12,32</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,76; 10,95</t>
+          <t>8,73; 10,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,24; 12,39</t>
+          <t>11,3; 12,49</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,28</t>
+          <t>10,9; 13,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,42; 11,26</t>
+          <t>8,58; 11,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 12,3</t>
+          <t>10,37; 12,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,08; 12,36</t>
+          <t>11,05; 12,35</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,89; 10,67</t>
+          <t>8,84; 10,51</t>
         </is>
       </c>
     </row>
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,21; 16,29</t>
+          <t>12,22; 16,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,58; 12,07</t>
+          <t>9,51; 12,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,41</t>
+          <t>8,26; 11,41</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,47</t>
+          <t>7,91; 12,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,26</t>
+          <t>10,22; 12,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,83; 9,53</t>
+          <t>6,63; 9,38</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 13,29</t>
+          <t>9,73; 13,23</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,16; 11,81</t>
+          <t>10,22; 11,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,82; 10,14</t>
+          <t>7,72; 10,06</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,37</t>
+          <t>11,29; 15,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 19,55</t>
+          <t>10,76; 19,63</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,12; 10,55</t>
+          <t>7,0; 10,42</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,97; 12,29</t>
+          <t>9,71; 12,39</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,77; 12,27</t>
+          <t>10,69; 12,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,3; 10,59</t>
+          <t>8,36; 10,66</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,84</t>
+          <t>10,79; 12,99</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,14; 16,58</t>
+          <t>11,23; 17,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 10,16</t>
+          <t>7,94; 9,99</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,49; 12,02</t>
+          <t>10,45; 12,02</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,77; 12,08</t>
+          <t>10,8; 12,01</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,18; 10,46</t>
+          <t>9,14; 10,35</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,67; 11,84</t>
+          <t>10,73; 11,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,68; 11,65</t>
+          <t>10,69; 11,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,88; 10,25</t>
+          <t>8,88; 10,22</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,81; 11,73</t>
+          <t>10,82; 11,76</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,84; 11,64</t>
+          <t>10,88; 11,7</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,21; 10,09</t>
+          <t>9,17; 10,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,81; 11,57</t>
+          <t>7,91; 11,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,24; 12,15</t>
+          <t>10,28; 12,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,75; 10,32</t>
+          <t>7,78; 10,5</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,42; 13,05</t>
+          <t>10,5; 13,17</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,52; 11,67</t>
+          <t>9,53; 11,69</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,86; 10,2</t>
+          <t>6,89; 10,14</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,45; 11,82</t>
+          <t>9,63; 11,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,19; 11,61</t>
+          <t>10,15; 11,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,53; 9,72</t>
+          <t>7,64; 9,89</t>
         </is>
       </c>
     </row>
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,94</t>
+          <t>8,13; 10,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,28; 12,32</t>
+          <t>9,25; 12,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,19</t>
+          <t>9,03; 12,34</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 12,94</t>
+          <t>10,17; 12,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 10,73</t>
+          <t>8,41; 10,7</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,33; 11,58</t>
+          <t>9,35; 11,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,79; 11,89</t>
+          <t>9,77; 11,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,13; 11,12</t>
+          <t>9,12; 11,03</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,53; 11,56</t>
+          <t>9,59; 11,45</t>
         </is>
       </c>
     </row>
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,86; 12,73</t>
+          <t>9,92; 12,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,74; 12,74</t>
+          <t>9,73; 12,65</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,5; 12,0</t>
+          <t>8,63; 12,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,59; 12,34</t>
+          <t>9,56; 12,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,04</t>
+          <t>10,74; 12,05</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,38; 15,49</t>
+          <t>10,19; 15,3</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,17; 12,06</t>
+          <t>10,21; 12,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,55; 12,02</t>
+          <t>10,54; 12,09</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,11; 12,93</t>
+          <t>10,15; 12,92</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,55; 12,6</t>
+          <t>9,2; 12,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,78; 12,32</t>
+          <t>10,73; 12,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,73; 10,94</t>
+          <t>8,7; 10,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 12,49</t>
+          <t>11,23; 12,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,9; 13,26</t>
+          <t>10,96; 13,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,58; 11,26</t>
+          <t>8,44; 11,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,37; 12,32</t>
+          <t>10,41; 12,29</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,05; 12,35</t>
+          <t>11,07; 12,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,84; 10,51</t>
+          <t>8,81; 10,55</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,51; 12,03</t>
+          <t>9,63; 12,12</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1132,32 +1132,32 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,54</t>
+          <t>7,91; 12,33</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 12,32</t>
+          <t>10,25; 12,2</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,63; 9,38</t>
+          <t>6,7; 9,48</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,73; 13,23</t>
+          <t>9,75; 13,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,22; 11,82</t>
+          <t>10,15; 11,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,72; 10,06</t>
+          <t>7,94; 10,11</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,29; 15,27</t>
+          <t>11,33; 15,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,76; 19,63</t>
+          <t>10,75; 19,47</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,42</t>
+          <t>7,0; 10,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,71; 12,39</t>
+          <t>9,69; 12,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,69; 12,28</t>
+          <t>10,88; 12,28</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,36; 10,66</t>
+          <t>8,31; 10,61</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,79; 12,99</t>
+          <t>10,74; 12,86</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,23; 17,24</t>
+          <t>11,25; 16,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,94; 9,99</t>
+          <t>7,93; 9,98</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,45; 12,02</t>
+          <t>10,41; 12,05</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,8; 12,01</t>
+          <t>10,75; 12,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,14; 10,35</t>
+          <t>9,12; 10,29</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,73; 11,91</t>
+          <t>10,72; 11,89</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,69; 11,66</t>
+          <t>10,7; 11,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,88; 10,22</t>
+          <t>8,89; 10,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,82; 11,76</t>
+          <t>10,78; 11,74</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 11,7</t>
+          <t>10,88; 11,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,17; 10,13</t>
+          <t>9,25; 10,09</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IQ3005_MoAR-Clase-trans_orig.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>10,71</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>8,56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>9,97</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>11,23</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>8,92</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,59</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,71</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>8,56</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,91; 11,44</t>
+          <t>10,39; 13,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>10,28; 12,11</t>
+          <t>9,58; 11,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7,78; 10,5</t>
+          <t>6,86; 10,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,5; 13,17</t>
+          <t>8,01; 11,63</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,53; 11,69</t>
+          <t>10,27; 12,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,89; 10,14</t>
+          <t>7,7; 10,42</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,63; 11,89</t>
+          <t>9,62; 11,92</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 11,64</t>
+          <t>10,18; 11,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,64; 9,89</t>
+          <t>7,65; 9,77</t>
         </is>
       </c>
     </row>
@@ -734,32 +734,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>11,48</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9,62</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>10,49</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,54</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,57</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>10,42</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>11,48</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>9,62</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>10,49</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -787,47 +787,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,13; 10,83</t>
+          <t>10,15; 12,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9,25; 12,22</t>
+          <t>8,34; 10,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>9,03; 12,34</t>
+          <t>9,38; 11,57</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,17; 12,95</t>
+          <t>8,03; 10,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,41; 10,7</t>
+          <t>9,26; 12,37</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,35; 11,61</t>
+          <t>9,02; 12,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 11,8</t>
+          <t>9,82; 11,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,03</t>
+          <t>9,2; 11,14</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,59; 11,45</t>
+          <t>9,54; 11,5</t>
         </is>
       </c>
     </row>
@@ -844,32 +844,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>11,5</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>12,02</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>11,36</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>10,86</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>10,74</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>11,0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,5</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>12,02</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -897,47 +897,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9,92; 12,69</t>
+          <t>9,62; 12,18</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,65</t>
+          <t>10,71; 12,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,63; 12,0</t>
+          <t>10,43; 15,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 12,18</t>
+          <t>9,82; 12,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>10,74; 12,05</t>
+          <t>9,66; 12,9</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>10,19; 15,3</t>
+          <t>8,51; 12,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>10,21; 12,08</t>
+          <t>10,2; 12,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,54; 12,09</t>
+          <t>10,52; 11,99</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>10,15; 12,92</t>
+          <t>10,07; 12,9</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,92</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>11,88</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>9,71</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>11,35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>11,43</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>9,58</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11,92</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,88</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>9,71</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1007,47 +1007,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,51</t>
+          <t>11,24; 12,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,73; 12,21</t>
+          <t>10,96; 13,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,7; 10,84</t>
+          <t>8,42; 11,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,23; 12,47</t>
+          <t>9,31; 12,52</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,96; 13,45</t>
+          <t>10,79; 12,25</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,44; 11,27</t>
+          <t>8,76; 10,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,29</t>
+          <t>10,42; 12,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,07; 12,42</t>
+          <t>11,08; 12,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,81; 10,55</t>
+          <t>8,89; 10,67</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>10,25</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>11,26</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>8,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>13,6</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>10,75</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>10,42</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>10,25</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>11,26</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8,14</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1117,47 +1117,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 16,6</t>
+          <t>7,97; 12,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,12</t>
+          <t>10,2; 12,26</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>8,26; 11,41</t>
+          <t>6,83; 9,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,91; 12,33</t>
+          <t>12,21; 16,29</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,25; 12,2</t>
+          <t>9,58; 12,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,7; 9,48</t>
+          <t>8,52; 11,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,75; 13,2</t>
+          <t>9,94; 13,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,15; 11,82</t>
+          <t>10,16; 11,81</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,94; 10,11</t>
+          <t>7,82; 10,14</t>
         </is>
       </c>
     </row>
@@ -1174,32 +1174,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11,31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>11,66</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9,33</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>12,56</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>13,73</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8,69</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11,31</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>11,66</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>9,33</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1227,47 +1227,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,33; 15,34</t>
+          <t>9,97; 12,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10,75; 19,47</t>
+          <t>10,77; 12,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,0; 10,46</t>
+          <t>8,3; 10,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9,69; 12,3</t>
+          <t>11,33; 15,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>10,88; 12,28</t>
+          <t>10,75; 19,55</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8,31; 10,61</t>
+          <t>7,12; 10,55</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,74; 12,86</t>
+          <t>10,78; 12,84</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>11,25; 16,61</t>
+          <t>11,14; 16,58</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7,93; 9,98</t>
+          <t>7,93; 10,16</t>
         </is>
       </c>
     </row>
@@ -1284,32 +1284,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>11,3</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11,13</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9,55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>11,27</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>11,29</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>9,71</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>11,3</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>11,13</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>9,55</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1337,47 +1337,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>10,41; 12,05</t>
+          <t>10,67; 11,84</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,75; 12,0</t>
+          <t>10,68; 11,65</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,12; 10,29</t>
+          <t>8,88; 10,25</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,72; 11,89</t>
+          <t>10,49; 12,02</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,7; 11,65</t>
+          <t>10,77; 12,08</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,89; 10,17</t>
+          <t>9,18; 10,46</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,78; 11,74</t>
+          <t>10,81; 11,73</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,88; 11,63</t>
+          <t>10,84; 11,64</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>9,25; 10,09</t>
+          <t>9,21; 10,09</t>
         </is>
       </c>
     </row>
